--- a/ksoft_old/docs/fields_details/jalmeida/IN0518.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/IN0518.xlsx
@@ -2103,13 +2103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D311E6-BFEC-4669-BAD3-D88D5C182F39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AECA432D-D2E0-449B-AD1C-B7356E41B092}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A60CC66-1779-4788-93E6-EE1C85978667}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FBB863E-E39E-46A3-9779-406F500B343B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5170922-2413-426C-83AD-2564D202ADEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8743328-492D-4038-85D4-230916A01D59}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/IN0518.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/IN0518.xlsx
@@ -2103,13 +2103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AECA432D-D2E0-449B-AD1C-B7356E41B092}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D58FEA9B-4384-4B7F-AACB-1AD5D6351356}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FBB863E-E39E-46A3-9779-406F500B343B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC4A50E3-D59B-4E5C-BCC0-83DE49B7323A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8743328-492D-4038-85D4-230916A01D59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C46573-CEA0-493E-A088-ED14134A7176}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/IN0518.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/IN0518.xlsx
@@ -2103,13 +2103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D58FEA9B-4384-4B7F-AACB-1AD5D6351356}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D311E6-BFEC-4669-BAD3-D88D5C182F39}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC4A50E3-D59B-4E5C-BCC0-83DE49B7323A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A60CC66-1779-4788-93E6-EE1C85978667}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C46573-CEA0-493E-A088-ED14134A7176}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5170922-2413-426C-83AD-2564D202ADEE}"/>
 </file>